--- a/docs/ccprecampojuridico.xlsx
+++ b/docs/ccprecampojuridico.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\brandon.mata\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3DC00BDE-C0C4-414A-91EA-8F480C09BBE2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A9905C7-6050-47FD-B658-82B6DE4E12D9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11505" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -98,7 +98,7 @@
     <t>Corrección de Calidad Extraordinaria</t>
   </si>
   <si>
-    <t>Producción Horas Extra</t>
+    <t>Producción Horas Extras</t>
   </si>
 </sst>
 </file>
